--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -991,7 +991,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2022-01-18</t>
+          <t>2022-01-19</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2023-03-16</t>
+          <t>2023-03-17</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2022-12-21</t>
+          <t>2022-12-22</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2023-02-05</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2022-02-21</t>
+          <t>2022-02-22</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-02</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2022-11-07</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-12-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2022-03-14</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2020-11-02</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2022-01-30</t>
+          <t>2022-01-31</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
+          <t>2023-02-20</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2021-08-26</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7816,7 +7816,7 @@
           <t>A | 3361呎 (4+房)
 $24115万
 $71,749/呎
-(22年-07月-13日)</t>
+(22年-07月-14日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -7838,7 +7838,7 @@
           <t>A | 578呎 (2房)
 $2563万
 $44,336/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -7846,7 +7846,7 @@
           <t>B | 522呎 (2房)
 $1892万
 $36,253/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -7854,7 +7854,7 @@
           <t>C | 342呎 (1房)
 $1307万
 $38,219/呎
-(24年-04月-18日)</t>
+(24年-04月-19日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -7871,7 +7871,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -7902,7 +7902,7 @@
           <t>A | 578呎 (2房)
 $1954万
 $33,810/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -7910,7 +7910,7 @@
           <t>B | 522呎 (2房)
 $2122万
 $40,653/呎
-(25年-05月-12日)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -7918,7 +7918,7 @@
           <t>C | 342呎 (1房)
 $1281万
 $37,468/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -7935,7 +7935,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -7943,7 +7943,7 @@
           <t>G | 535呎 (null房)
 $6951万
 $129,927/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -7951,7 +7951,7 @@
           <t>H | 1257呎 (null房)
 $6951万
 $55,299/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
           <t>A | 578呎 (2房)
 $2372万
 $41,029/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -7974,7 +7974,7 @@
           <t>B | 522呎 (2房)
 $2060万
 $39,469/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -7982,7 +7982,7 @@
           <t>C | 342呎 (1房)
 $1256万
 $36,731/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -7999,7 +7999,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -8030,7 +8030,7 @@
           <t>A | 578呎 (2房)
 $2302万
 $39,834/呎
-(24年-09月-04日)</t>
+(24年-09月-05日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -8038,7 +8038,7 @@
           <t>B | 522呎 (2房)
 $2037万
 $39,027/呎
-(24年-09月-04日)</t>
+(24年-09月-05日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -8046,7 +8046,7 @@
           <t>C | 342呎 (1房)
 $1232万
 $36,009/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -8054,7 +8054,7 @@
           <t>D | 842呎 (3房)
 $3482万
 $41,355/呎
-(24年-04月-16日)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
@@ -8063,7 +8063,7 @@
           <t>F | 551呎 (2房)
 $2490万
 $45,181/呎
-(24年-07月-17日)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -8071,7 +8071,7 @@
           <t>G | 535呎 (2房)
 $2413万
 $45,095/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -8079,7 +8079,7 @@
           <t>H | 1257呎 (4+房)
 $4570万
 $36,352/呎
-(25年-03月-10日)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
           <t>A | 578呎 (2房)
 $2220万
 $38,408/呎
-(24年-06月-16日)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -8102,7 +8102,7 @@
           <t>B | 522呎 (2房)
 $1978万
 $37,889/呎
-(24年-09月-18日)</t>
+(24年-09月-19日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8110,7 +8110,7 @@
           <t>C | 342呎 (1房)
 $1207万
 $35,301/呎
-(24年-04月-16日)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -8118,7 +8118,7 @@
           <t>D | 842呎 (3房)
 $3073万
 $36,500/呎
-(21年-12月-22日)</t>
+(21年-12月-23日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -8127,7 +8127,7 @@
           <t>F | 551呎 (2房)
 $2441万
 $44,294/呎
-(24年-06月-24日)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -8135,7 +8135,7 @@
           <t>G | 535呎 (2房)
 $2365万
 $44,209/呎
-(24年-06月-24日)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="I10" s="24" t="inlineStr">
@@ -8158,7 +8158,7 @@
           <t>A | 578呎 (2房)
 $1970万
 $34,087/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -8166,7 +8166,7 @@
           <t>B | 522呎 (2房)
 $1920万
 $36,785/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
@@ -8191,7 +8191,7 @@
           <t>F | 551呎 (2房)
 $2349万
 $42,635/呎
-(24年-07月-15日)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -8199,7 +8199,7 @@
           <t>G | 535呎 (2房)
 $2277万
 $42,553/呎
-(24年-07月-03日)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -8207,7 +8207,7 @@
           <t>H | 1257呎 (4+房)
 $3475万
 $27,645/呎
-(23年-02月-27日)</t>
+(23年-02月-28日)</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
           <t>B | 522呎 (2房)
 $1440万
 $27,596/呎
-(23年-11月-23日)</t>
+(23年-11月-24日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8238,7 +8238,7 @@
           <t>C | 342呎 (1房)
 $1064万
 $31,102/呎
-(22年-01月-18日)</t>
+(22年-01月-19日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -8246,7 +8246,7 @@
           <t>D | 842呎 (3房)
 $2922万
 $34,700/呎
-(22年-03月-31日)</t>
+(22年-04月-01日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -8255,7 +8255,7 @@
           <t>F | 551呎 (2房)
 $2303万
 $41,797/呎
-(24年-07月-15日)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -8263,7 +8263,7 @@
           <t>G | 535呎 (2房)
 $1900万
 $35,514/呎
-(23年-04月-17日)</t>
+(23年-04月-18日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -8271,7 +8271,7 @@
           <t>H | 1257呎 (4+房)
 $3507万
 $27,901/呎
-(23年-02月-01日)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
           <t>A | 578呎 (2房)
 $1634万
 $28,265/呎
-(23年-10月-10日)</t>
+(23年-10月-11日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -8294,7 +8294,7 @@
           <t>B | 522呎 (2房)
 $1561万
 $29,910/呎
-(22年-12月-21日)</t>
+(22年-12月-22日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -8302,7 +8302,7 @@
           <t>C | 342呎 (1房)
 $1014万
 $29,661/呎
-(23年-04月-18日)</t>
+(23年-04月-19日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -8310,7 +8310,7 @@
           <t>D | 842呎 (3房)
 $2854万
 $33,900/呎
-(21年-05月-06日)</t>
+(21年-05月-07日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -8319,7 +8319,7 @@
           <t>F | 551呎 (2房)
 $1777万
 $32,249/呎
-(24年-04月-07日)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -8335,7 +8335,7 @@
           <t>H | 1257呎 (4+房)
 $3368万
 $26,796/呎
-(23年-03月-16日)</t>
+(23年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
           <t>A | 578呎 (2房)
 $1714万
 $29,649/呎
-(23年-03月-20日)</t>
+(23年-03月-21日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -8358,7 +8358,7 @@
           <t>B | 522呎 (2房)
 $1538万
 $29,467/呎
-(21年-12月-15日)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8366,7 +8366,7 @@
           <t>C | 342呎 (1房)
 $1000万
 $29,225/呎
-(23年-03月-20日)</t>
+(23年-03月-21日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -8374,7 +8374,7 @@
           <t>D | 842呎 (3房)
 $2745万
 $32,600/呎
-(21年-04月-27日)</t>
+(21年-04月-28日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -8383,7 +8383,7 @@
           <t>F | 551呎 (2房)
 $1742万
 $31,617/呎
-(23年-06月-05日)</t>
+(23年-06月-06日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -8391,7 +8391,7 @@
           <t>G | 535呎 (2房)
 $1817万
 $33,970/呎
-(23年-07月-17日)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -8399,7 +8399,7 @@
           <t>H | 1257呎 (4+房)
 $3360万
 $26,730/呎
-(23年-02月-05日)</t>
+(23年-02月-06日)</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8414,7 @@
           <t>A | 579呎 (2房)
 $1688万
 $29,161/呎
-(21年-08月-10日)</t>
+(21年-08月-11日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -8422,7 +8422,7 @@
           <t>B | 522呎 (2房)
 $1467万
 $28,098/呎
-(21年-12月-01日)</t>
+(21年-12月-02日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -8430,7 +8430,7 @@
           <t>C | 342呎 (1房)
 $985万
 $28,789/呎
-(21年-12月-07日)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -8438,7 +8438,7 @@
           <t>D | 842呎 (3房)
 $2829万
 $33,600/呎
-(22年-02月-21日)</t>
+(22年-02月-22日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
           <t>F | 551呎 (2房)
 $1898万
 $34,437/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -8455,7 +8455,7 @@
           <t>G | 535呎 (2房)
 $1821万
 $34,032/呎
-(22年-01月-12日)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -8463,7 +8463,7 @@
           <t>H | 1257呎 (4+房)
 $3300万
 $26,253/呎
-(23年-06月-12日)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
           <t>A | 579呎 (2房)
 $1562万
 $26,983/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -8486,7 +8486,7 @@
           <t>B | 522呎 (2房)
 $1357万
 $26,002/呎
-(21年-04月-27日)</t>
+(21年-04月-28日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8494,7 +8494,7 @@
           <t>C | 342呎 (1房)
 $985万
 $28,789/呎
-(22年-11月-07日)</t>
+(22年-11月-08日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -8502,7 +8502,7 @@
           <t>D | 842呎 (3房)
 $2745万
 $32,601/呎
-(22年-03月-31日)</t>
+(22年-04月-01日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -8511,7 +8511,7 @@
           <t>F | 551呎 (2房)
 $1674万
 $30,388/呎
-(24年-03月-24日)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -8519,7 +8519,7 @@
           <t>G | 535呎 (2房)
 $1623万
 $30,333/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -8527,7 +8527,7 @@
           <t>H | 1257呎 (4+房)
 $3500万
 $27,844/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
           <t>A | 578呎 (2房)
 $1532万
 $26,500/呎
-(24年-05月-01日)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -8550,7 +8550,7 @@
           <t>B | 522呎 (2房)
 $1331万
 $25,490/呎
-(21年-05月-05日)</t>
+(21年-05月-06日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -8558,7 +8558,7 @@
           <t>C | 342呎 (1房)
 $983万
 $28,731/呎
-(22年-01月-12日)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -8566,7 +8566,7 @@
           <t>D | 527呎 (2房)
 $1612万
 $30,584/呎
-(22年-03月-14日)</t>
+(22年-03月-15日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -8574,7 +8574,7 @@
           <t>E | 332呎 (1房)
 $995万
 $29,961/呎
-(20年-11月-04日)</t>
+(20年-11月-05日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -8582,7 +8582,7 @@
           <t>F | 552呎 (2房)
 $1792万
 $32,455/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -8590,7 +8590,7 @@
           <t>G | 535呎 (2房)
 $1733万
 $32,393/呎
-(21年-12月-30日)</t>
+(21年-12月-31日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -8598,7 +8598,7 @@
           <t>H | 1257呎 (4+房)
 $3050万
 $24,264/呎
-(23年-01月-09日)</t>
+(23年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
           <t>A | 579呎 (2房)
 $1604万
 $27,698/呎
-(20年-11月-01日)</t>
+(20年-11月-02日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -8621,7 +8621,7 @@
           <t>B | 522呎 (2房)
 $1273万
 $24,393/呎
-(20年-11月-03日)</t>
+(20年-11月-04日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8629,7 +8629,7 @@
           <t>C | 342呎 (1房)
 $895万
 $26,170/呎
-(20年-11月-03日)</t>
+(20年-11月-04日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -8637,7 +8637,7 @@
           <t>D | 527呎 (2房)
 $1599万
 $30,340/呎
-(22年-01月-30日)</t>
+(22年-01月-31日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -8645,7 +8645,7 @@
           <t>E | 332呎 (1房)
 $966万
 $29,087/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -8653,7 +8653,7 @@
           <t>F | 552呎 (2房)
 $1684万
 $30,498/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -8661,7 +8661,7 @@
           <t>G | 535呎 (2房)
 $1602万
 $29,936/呎
-(20年-11月-02日)</t>
+(20年-11月-03日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -8669,7 +8669,7 @@
           <t>H | 1257呎 (4+房)
 $3400万
 $27,049/呎
-(22年-10月-31日)</t>
+(22年-11月-01日)</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
           <t>A | 578呎 (2房)
 $1403万
 $24,266/呎
-(21年-04月-08日)</t>
+(21年-04月-09日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -8692,7 +8692,7 @@
           <t>B | 522呎 (2房)
 $1218万
 $23,343/呎
-(21年-04月-21日)</t>
+(21年-04月-22日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -8700,7 +8700,7 @@
           <t>C | 342呎 (1房)
 $856万
 $25,044/呎
-(20年-11月-03日)</t>
+(20年-11月-04日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -8708,7 +8708,7 @@
           <t>D | 527呎 (2房)
 $1454万
 $27,583/呎
-(24年-05月-01日)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -8716,7 +8716,7 @@
           <t>E | 332呎 (1房)
 $1028万
 $30,970/呎
-(21年-08月-26日)</t>
+(21年-08月-27日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -8724,7 +8724,7 @@
           <t>F | 552呎 (2房)
 $1581万
 $28,645/呎
-(23年-10月-24日)</t>
+(23年-10月-25日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -8732,7 +8732,7 @@
           <t>G | 535呎 (2房)
 $1661万
 $31,049/呎
-(23年-02月-19日)</t>
+(23年-02月-20日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -8740,7 +8740,7 @@
           <t>H | 1257呎 (4+房)
 $2950万
 $23,469/呎
-(23年-02月-07日)</t>
+(23年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
           <t>A | 556呎 (2房)
 $1268万
 $22,806/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -8763,7 +8763,7 @@
           <t>B | 521呎 (2房)
 $1164万
 $22,338/呎
-(21年-04月-25日)</t>
+(21年-04月-26日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -8771,7 +8771,7 @@
           <t>C | 342呎 (1房)
 $783万
 $22,889/呎
-(20年-11月-01日)</t>
+(20年-11月-02日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -8779,7 +8779,7 @@
           <t>D | 527呎 (2房)
 $1503万
 $28,514/呎
-(22年-07月-06日)</t>
+(22年-07月-07日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -8787,7 +8787,7 @@
           <t>E | 331呎 (1房)
 $910万
 $27,502/呎
-(21年-03月-31日)</t>
+(21年-04月-01日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -8795,7 +8795,7 @@
           <t>F | 552呎 (2房)
 $1587万
 $28,746/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -8803,7 +8803,7 @@
           <t>G | 534呎 (2房)
 $1442万
 $27,000/呎
-(21年-04月-12日)</t>
+(21年-04月-13日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -8811,7 +8811,7 @@
           <t>H | 1257呎 (4+房)
 $3300万
 $26,253/呎
-(22年-10月-31日)</t>
+(22年-11月-01日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -3266,38 +3266,30 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>25800000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>30641</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K42" s="5" t="n">
+        <v>25800000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>30641</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3306,7 +3298,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7726,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7744,7 +7736,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8177,12 +8169,12 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 842呎 (3房)
-招标单位
--
-(在售)</t>
+$2580万
+$30,641/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>

--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -1746,7 +1746,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7726,27 +7726,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7994,20 +7994,20 @@
 (26年-06月-03日)</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>G | 534呎 (2房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 1258呎 (4+房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>H | 1258呎 (4+房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
